--- a/examples/收件人清单导入模板.xlsx
+++ b/examples/收件人清单导入模板.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="收件人清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +50,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,10 +418,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -424,53 +429,77 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>收件人名称</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>水印名称</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>收件人</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>抄送</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>密送</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>邮件标题</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>附件路径</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>合并组</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>打开口令</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>权限口令</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Call_Amount</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Unfunded</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Due_Date</t>
         </is>
       </c>
     </row>
@@ -507,17 +536,243 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C:\Document\补充说明.pdf（多个用;分隔，可留空）</t>
+          <t>C:\Document\补充说明.pdf（每人专属；多个用;分隔，可留空）</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>（留空=不合并）</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>（留空=自动生成）</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>（留空=自动生成，勿发给对方）</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>（留空=自动生成，勿发给LP）</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>200,000</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>800,000</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>列名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>收件人名称</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>收件单位全称；识别依据，也是水印默认文字</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>水印名称</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>留空 = 同收件人名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>收件人</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>收件邮箱；多个用 ; 分隔（英文逗号是文件名的一部分，不做分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>抄送 / 密送</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>邮箱；多个用 ; 分隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>邮件标题</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>留空 = 用邮件模板里的主题</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>附件路径</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>这一位收件人专属要附的文件（本地路径，多个用 ; 分隔）；会自动进这个人的附件包</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>合并组</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>仅「按组合并」发送模式生效；同组共用一封邮件、附件包合并</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>打开口令</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>留空 = 自动生成随机口令（收件人打开文件用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>权限口令</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>留空 = 自动生成（控制打印权限，绝不会进入邮件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>其它任意列</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>作为自定义字段收进收件人，可在流水线的字段映射里用到</t>
         </is>
       </c>
     </row>

--- a/examples/收件人清单导入模板.xlsx
+++ b/examples/收件人清单导入模板.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -427,13 +427,12 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,35 +468,30 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>附件路径</t>
+          <t>合并组</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>合并组</t>
+          <t>打开口令</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>打开口令</t>
+          <t>权限口令</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>权限口令</t>
+          <t>Call_Amount</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Call_Amount</t>
+          <t>Unfunded</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Unfunded</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Due_Date</t>
         </is>
@@ -536,35 +530,30 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C:\Document\补充说明.pdf（每人专属；多个用;分隔，可留空）</t>
+          <t>（留空=不合并）</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>（留空=不合并）</t>
+          <t>（留空=自动生成）</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>（留空=自动生成）</t>
+          <t>（留空=自动生成，勿发给LP）</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>（留空=自动生成，勿发给LP）</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
-        <is>
-          <t>800,000</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
         <is>
           <t>2026-11-15</t>
         </is>
@@ -581,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -694,7 +683,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>附件路径</t>
+          <t>打开口令</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -704,14 +693,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>这一位收件人专属要附的文件（本地路径，多个用 ; 分隔）；会自动进这个人的附件包</t>
+          <t>留空 = 自动生成随机口令（收件人打开文件用）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>合并组</t>
+          <t>权限口令</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -721,14 +710,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>仅「按组合并」发送模式生效；同组共用一封邮件、附件包合并</t>
+          <t>留空 = 自动生成（控制打印权限，绝不会进入邮件）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>打开口令</t>
+          <t>合并组</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -738,14 +727,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>留空 = 自动生成随机口令（收件人打开文件用）</t>
+          <t>仅「按组合并」发送模式生效；同组共用一封邮件、附件包合并</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>权限口令</t>
+          <t>其它任意列</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -754,23 +743,6 @@
         </is>
       </c>
       <c r="C10" t="inlineStr">
-        <is>
-          <t>留空 = 自动生成（控制打印权限，绝不会进入邮件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>其它任意列</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
         <is>
           <t>作为自定义字段收进收件人，可在流水线的字段映射里用到</t>
         </is>
